--- a/data/Сажида (русс)/3. Служебные слова.xlsx
+++ b/data/Сажида (русс)/3. Служебные слова.xlsx
@@ -45,9 +45,6 @@
     <t>مَا</t>
   </si>
   <si>
-    <t>От, Из</t>
-  </si>
-  <si>
     <t>Тоже, Также, Еще</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>بِ</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>До свидания!</t>
   </si>
   <si>
@@ -94,6 +88,12 @@
   </si>
   <si>
     <t>Имя</t>
+  </si>
+  <si>
+    <t>От, Из  (предлог)</t>
+  </si>
+  <si>
+    <t>C  (предлог)</t>
   </si>
 </sst>
 </file>
@@ -487,10 +487,10 @@
     </row>
     <row r="5" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1"/>
       <c r="I5" s="1"/>
@@ -498,10 +498,10 @@
     </row>
     <row r="6" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1"/>
       <c r="I6" s="1"/>
@@ -512,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1"/>
       <c r="I7" s="1"/>
@@ -520,56 +520,56 @@
     </row>
     <row r="8" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1"/>
     </row>
